--- a/public/assets/mohreport/DrOutstanding.xlsx
+++ b/public/assets/mohreport/DrOutstanding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cmas\REPORT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\msoftweb\public\assets\mohreport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D82F0F85-B165-40FC-B3E9-D66FE53B2E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD20E9E-B8FC-40B0-AFBB-D14167BD9FC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" xr2:uid="{F31F1418-9D1F-403F-A93E-1B72F8145E5A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23715" windowHeight="8085" activeTab="1" xr2:uid="{F31F1418-9D1F-403F-A93E-1B72F8145E5A}"/>
   </bookViews>
   <sheets>
     <sheet name="ANISS" sheetId="4" r:id="rId1"/>
@@ -18,18 +18,10 @@
     <sheet name="AMIN" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -41,9 +33,6 @@
     <t>DOCTOR : AMIN DR. MOHD AMIN BIN MOHD MOKHTAR</t>
   </si>
   <si>
-    <t>UITM PRIVATE HEALTHCARE SDN BHD</t>
-  </si>
-  <si>
     <t>CONSULTANT CHARGES OUTSTANDING LISTING</t>
   </si>
   <si>
@@ -366,6 +355,9 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>ABC MEDICAL SPECIALIST CENTRE</t>
   </si>
 </sst>
 </file>
@@ -373,7 +365,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -418,7 +410,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -439,11 +431,11 @@
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -772,72 +764,72 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I1" s="2" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="O5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -848,19 +840,19 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8">
         <v>14895</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8">
         <v>2210</v>
@@ -869,13 +861,13 @@
         <v>5</v>
       </c>
       <c r="H8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>108</v>
-      </c>
       <c r="J8" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K8" s="6">
         <v>146</v>
@@ -915,7 +907,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -958,7 +950,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -997,86 +989,86 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I1" s="2" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="M5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="C8">
         <v>112444</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8">
         <v>3573</v>
@@ -1085,13 +1077,13 @@
         <v>16</v>
       </c>
       <c r="H8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="K8" s="6">
         <v>6511.7</v>
@@ -1117,7 +1109,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1155,64 +1147,64 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I1" s="2" t="s">
-        <v>1</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="M5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="O5" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -1222,19 +1214,19 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="C8">
         <v>7798</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
       <c r="F8">
         <v>3191</v>
@@ -1243,13 +1235,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="K8" s="6">
         <v>2413.5</v>
@@ -1269,19 +1261,19 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>8121</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
       </c>
       <c r="F9">
         <v>2494</v>
@@ -1290,13 +1282,13 @@
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K9">
         <v>237.05</v>
@@ -1316,19 +1308,19 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>8741</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
       </c>
       <c r="F10">
         <v>2548</v>
@@ -1337,13 +1329,13 @@
         <v>3</v>
       </c>
       <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="K10" s="6">
         <v>2297.15</v>
@@ -1363,19 +1355,19 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>9602</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
         <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
       </c>
       <c r="F11">
         <v>3773</v>
@@ -1384,13 +1376,13 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K11">
         <v>253.45</v>
@@ -1410,19 +1402,19 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>10197</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
         <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
       </c>
       <c r="F12">
         <v>3931</v>
@@ -1431,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K12">
         <v>401.9</v>
@@ -1457,19 +1449,19 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>11093</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
         <v>22</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
       </c>
       <c r="F13">
         <v>4160</v>
@@ -1478,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="K13" s="6">
         <v>6172.15</v>
@@ -1504,19 +1496,19 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>11193</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
         <v>22</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
       </c>
       <c r="F14">
         <v>3084</v>
@@ -1525,13 +1517,13 @@
         <v>2</v>
       </c>
       <c r="H14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="K14">
         <v>275.95</v>
@@ -1551,19 +1543,19 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>11306</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
         <v>22</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
       </c>
       <c r="F15">
         <v>2840</v>
@@ -1572,13 +1564,13 @@
         <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K15" s="6">
         <v>3986.6</v>
@@ -1598,19 +1590,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>11943</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
         <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
       </c>
       <c r="F16">
         <v>1439</v>
@@ -1619,13 +1611,13 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K16">
         <v>185.8</v>
@@ -1645,19 +1637,19 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>11944</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
         <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
       </c>
       <c r="F17">
         <v>2862</v>
@@ -1666,13 +1658,13 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K17">
         <v>332.3</v>
@@ -1692,19 +1684,19 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>12792</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18">
         <v>4801</v>
@@ -1713,13 +1705,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18">
         <v>164.85</v>
@@ -1739,19 +1731,19 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>12814</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
         <v>22</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
       </c>
       <c r="F19">
         <v>3084</v>
@@ -1760,13 +1752,13 @@
         <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" s="6">
         <v>1312.95</v>
@@ -1786,19 +1778,19 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>13134</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
         <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>23</v>
       </c>
       <c r="F20">
         <v>3250</v>
@@ -1807,13 +1799,13 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="K20">
         <v>488</v>
@@ -1833,19 +1825,19 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21">
         <v>13550</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
         <v>22</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
       </c>
       <c r="F21">
         <v>1874</v>
@@ -1854,13 +1846,13 @@
         <v>6</v>
       </c>
       <c r="H21" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="K21" s="6">
         <v>2002.65</v>
@@ -1880,19 +1872,19 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22">
         <v>14279</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
         <v>22</v>
-      </c>
-      <c r="E22" t="s">
-        <v>23</v>
       </c>
       <c r="F22">
         <v>210</v>
@@ -1901,13 +1893,13 @@
         <v>4</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K22">
         <v>649.9</v>
@@ -1927,19 +1919,19 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23">
         <v>14279</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
         <v>22</v>
-      </c>
-      <c r="E23" t="s">
-        <v>23</v>
       </c>
       <c r="F23">
         <v>210</v>
@@ -1948,13 +1940,13 @@
         <v>4</v>
       </c>
       <c r="H23" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="J23" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K23">
         <v>649.9</v>
@@ -1974,19 +1966,19 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24">
         <v>14853</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" t="s">
         <v>22</v>
-      </c>
-      <c r="E24" t="s">
-        <v>23</v>
       </c>
       <c r="F24">
         <v>3400</v>
@@ -1995,13 +1987,13 @@
         <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K24">
         <v>289.8</v>
@@ -2021,19 +2013,19 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25">
         <v>15419</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
         <v>22</v>
-      </c>
-      <c r="E25" t="s">
-        <v>23</v>
       </c>
       <c r="F25">
         <v>2401</v>
@@ -2042,13 +2034,13 @@
         <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K25">
         <v>208.6</v>
@@ -2068,19 +2060,19 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C26">
         <v>15420</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
         <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>23</v>
       </c>
       <c r="F26">
         <v>2548</v>
@@ -2089,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K26">
         <v>433.35</v>
@@ -2115,19 +2107,19 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27">
         <v>15477</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s">
         <v>22</v>
-      </c>
-      <c r="E27" t="s">
-        <v>23</v>
       </c>
       <c r="F27">
         <v>4213</v>
@@ -2136,13 +2128,13 @@
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K27">
         <v>169.2</v>
@@ -2162,19 +2154,19 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C28">
         <v>15518</v>
       </c>
       <c r="D28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" t="s">
         <v>22</v>
-      </c>
-      <c r="E28" t="s">
-        <v>23</v>
       </c>
       <c r="F28">
         <v>4714</v>
@@ -2183,13 +2175,13 @@
         <v>9</v>
       </c>
       <c r="H28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K28">
         <v>801.9</v>
@@ -2209,16 +2201,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29">
         <v>31446</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E29">
         <v>10100</v>
@@ -2230,13 +2222,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K29" s="6">
         <v>1181.2</v>
@@ -2256,16 +2248,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30">
         <v>38978</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30">
         <v>6032</v>
@@ -2277,13 +2269,13 @@
         <v>14</v>
       </c>
       <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="K30" s="6">
         <v>5207.45</v>
@@ -2303,16 +2295,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31">
         <v>64016</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31">
         <v>18175</v>
@@ -2324,13 +2316,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="K31" s="6">
         <v>2579.4</v>
@@ -2350,19 +2342,19 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C32">
         <v>105659</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F32">
         <v>1396</v>
@@ -2371,13 +2363,13 @@
         <v>19</v>
       </c>
       <c r="H32" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="K32" s="6">
         <v>3981.65</v>
@@ -2397,19 +2389,19 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C33">
         <v>105659</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F33">
         <v>1396</v>
@@ -2418,13 +2410,13 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="K33" s="6">
         <v>3981.65</v>
@@ -2444,19 +2436,19 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C34">
         <v>105659</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F34">
         <v>1396</v>
@@ -2465,13 +2457,13 @@
         <v>19</v>
       </c>
       <c r="H34" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="K34" s="6">
         <v>3981.65</v>
@@ -2491,19 +2483,19 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35">
         <v>108228</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F35">
         <v>25157</v>
@@ -2512,13 +2504,13 @@
         <v>4</v>
       </c>
       <c r="H35" t="s">
+        <v>79</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="K35" s="6">
         <v>12127.5</v>
@@ -2538,19 +2530,19 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C36">
         <v>116000</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36">
         <v>27453</v>
@@ -2559,13 +2551,13 @@
         <v>2</v>
       </c>
       <c r="H36" t="s">
+        <v>83</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J36" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="K36" s="6">
         <v>54391.85</v>
@@ -2585,19 +2577,19 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C37">
         <v>117033</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37">
         <v>24467</v>
@@ -2606,13 +2598,13 @@
         <v>5</v>
       </c>
       <c r="H37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K37" s="6">
         <v>32674.55</v>
@@ -2632,19 +2624,19 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C38">
         <v>117033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F38">
         <v>24467</v>
@@ -2653,13 +2645,13 @@
         <v>5</v>
       </c>
       <c r="H38" t="s">
+        <v>87</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J38" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="K38" s="6">
         <v>32674.55</v>
@@ -2679,19 +2671,19 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C39">
         <v>117609</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F39">
         <v>27881</v>
@@ -2700,13 +2692,13 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
+        <v>91</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="K39" s="6">
         <v>3185.4</v>
@@ -2726,19 +2718,19 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40">
         <v>117609</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40">
         <v>27881</v>
@@ -2747,13 +2739,13 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
+        <v>91</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J40" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="K40" s="6">
         <v>3185.4</v>
@@ -2773,19 +2765,19 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41">
         <v>118036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41">
         <v>27938</v>
@@ -2794,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="K41" s="6">
         <v>4010.7</v>
@@ -2826,7 +2818,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
